--- a/AAII_Financials/Quarterly/GL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>GL</t>
   </si>
@@ -656,480 +656,493 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1599700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1559600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1519600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1513000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1481300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1480400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1466300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1455400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1440200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1416100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1415700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1384100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1326400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1321300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1335100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1297200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1291800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1302600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1297400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1287200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1271100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1266600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1228900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1195700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1180900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1133100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1136600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1141300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1130500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1119200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1064700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1083800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1084800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1070400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1056900</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1092500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1077800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1034100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>888200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1024800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1020600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>980500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>942200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>987400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>979400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>942300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>953500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>950000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>938000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>90100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>88000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>86200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>84500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>151200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>151600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>148000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>153000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>144900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>140800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>146200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>143800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>139300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>138400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>138200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>135800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>128500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>129500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>129100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>129600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>507200</v>
+      </c>
+      <c r="E10" s="3">
         <v>481900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>485600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>624800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>456500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>459800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>485800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>513200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>452800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>436800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>473300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>430600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>376400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>383300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1245000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1209200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1205600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1218100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1146200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1135600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1123100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1113600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1084000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1054900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1034700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>989300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>997300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1002900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>992300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>983400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>936200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>954300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>955700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>940800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>936900</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,8 +1180,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1274,8 +1288,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,115 +1398,121 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E14" s="3">
         <v>2200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>15800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2400</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>900</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>1100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1400</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>3100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>9300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>4800</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>600</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>3300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2900</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>5500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>5900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>2000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1500,7 +1523,7 @@
         <v>7500</v>
       </c>
       <c r="F15" s="3">
-        <v>6800</v>
+        <v>7500</v>
       </c>
       <c r="G15" s="3">
         <v>6800</v>
@@ -1512,7 +1535,7 @@
         <v>6800</v>
       </c>
       <c r="J15" s="3">
-        <v>5300</v>
+        <v>6800</v>
       </c>
       <c r="K15" s="3">
         <v>5300</v>
@@ -1533,7 +1556,7 @@
         <v>5300</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1595,8 +1618,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1657,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1205500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1189300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1151200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>997200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1128500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1123200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1102400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1043700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1084100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1072600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1052400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1039300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1036100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1022200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1013700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1038500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>993500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>988500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1060100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1035500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1004100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1026600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>957500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>942500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>945800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>909300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>889000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>872900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>880300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>869800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>837500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>841000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>835500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>836000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>818800</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>394200</v>
+      </c>
+      <c r="E18" s="3">
         <v>370400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>368400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>515800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>352800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>357200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>363900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>411700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>356200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>343500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>363300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>344800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>290300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>299100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>321400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>258700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>298300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>314100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>237300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>251700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>267000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>240000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>271400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>253200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>235100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>223800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>247600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>268400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>250200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>249400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>227200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>242800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>249300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>234400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>238100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,8 +1917,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1928,8 +1962,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1991,53 +2025,56 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>401700</v>
+      </c>
+      <c r="E21" s="3">
         <v>377900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>375900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>522600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>359600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>364000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>370700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>416900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>361400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>348800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>368500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>350000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>295600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>304400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2098,329 +2135,341 @@
       <c r="AK21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E22" s="3">
         <v>34000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>35200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>36100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>34900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>35000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>35700</v>
-      </c>
-      <c r="J22" s="3">
-        <v>31400</v>
       </c>
       <c r="K22" s="3">
         <v>31400</v>
       </c>
       <c r="L22" s="3">
+        <v>31400</v>
+      </c>
+      <c r="M22" s="3">
         <v>28600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>26000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>25800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>24900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>24700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>24000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>20900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>21800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>21200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>21400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>21700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>22800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>20800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>20500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>21100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>21400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>21300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>23600</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>22400</v>
       </c>
       <c r="AI22" s="3">
         <v>22400</v>
       </c>
       <c r="AJ22" s="3">
+        <v>22400</v>
+      </c>
+      <c r="AK22" s="3">
         <v>21600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>21700</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>354900</v>
+      </c>
+      <c r="E23" s="3">
         <v>334100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>329500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>477100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>313300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>316100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>312400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>377000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>322300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>314900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>336700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>318800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>264500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>274200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>296700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>234800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>276400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>294200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>217600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>230800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>245200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>218800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>250000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>231500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>212200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>202900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>227100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>247300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>228800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>228100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>203600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>220300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>226900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>212800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>216400</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E24" s="3">
         <v>63600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>63400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>89300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>60600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>61500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>57200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>74000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>64000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>60700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>61900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>61700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>49200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>50600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>54400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>44200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>52500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>56700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>39600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>41900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>45600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>40300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>45700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>42600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>39200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>37400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>40000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>45500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>42200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>42700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>39700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>41600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>42500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>39100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>66000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2575,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>287700</v>
+      </c>
+      <c r="E26" s="3">
         <v>270500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>266100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>387800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>252700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>254600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>255200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>303000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>258400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>254200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>274800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>257100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>215300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>223600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>242300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>190600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>224000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>237500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>178000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>188900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>199600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>178500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>204200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>188900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>173000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>165500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>187100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>201800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>186600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>185400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>163900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>178700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>184400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>173700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>150400</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>287700</v>
+      </c>
+      <c r="E27" s="3">
         <v>270500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>266100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>387800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>252700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>254600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>255200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>303000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>258400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>254200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>274800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>257100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>215300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>223600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>242300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>190600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>224000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>237500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>178000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>188900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>199600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>178500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>204200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>188900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>173000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>165500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>187100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>201800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>186600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>185400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>163900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>178700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>184400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>173700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>150400</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2918,11 +2979,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -2940,22 +3001,25 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>800</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-100</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>877000</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,8 +3235,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3212,8 +3282,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3275,115 +3345,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>287700</v>
+      </c>
+      <c r="E33" s="3">
         <v>270500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>266100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>387800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>252700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>254600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>255200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>303000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>258400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>254200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>274800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>257100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>215300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>223600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>242300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>190600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>224000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>237500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>178000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>188900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>199600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>178500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>204200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>188900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>173000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>165500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>187100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>201800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>186600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>185300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>164700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>178700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>184400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>173600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1027300</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3565,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>287700</v>
+      </c>
+      <c r="E35" s="3">
         <v>270500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>266100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>387800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>252700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>254600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>255200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>303000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>258400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>254200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>274800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>257100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>215300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>223600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>242300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>190600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>224000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>237500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>178000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>188900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>199600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>178500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>204200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>188900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>173000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>165500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>187100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>201800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>186600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>185300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>164700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>178700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>184400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>173600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1027300</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,160 +3872,164 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>257100</v>
+      </c>
+      <c r="E41" s="3">
         <v>255200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>144700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>302700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>239100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>232300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>165300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>134500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>87900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>83500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>103200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>85500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>75000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>172100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>92600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>85600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>172300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>127600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>92200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>96300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>138100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>81500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>94800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>80100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>114000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>90400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>75900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>66700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>89300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>67300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>121000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>77400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>82200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>88600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>118600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>198300</v>
+      </c>
+      <c r="E42" s="3">
         <v>183800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>314700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>62800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>116700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>134100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>85000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>100500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>100600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>58400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>81700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>83900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>71100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>74400</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4000,115 +4090,121 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>818800</v>
+      </c>
+      <c r="E43" s="3">
         <v>727500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>768600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>729200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>690700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>691500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>691900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>651900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>648100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>646000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>630200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>616900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>601800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>594400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>589200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>475400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>478600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>487900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>487400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>485500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>484400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>477600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>474200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>458400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>445500</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>441700</v>
       </c>
       <c r="AC43" s="3">
         <v>441700</v>
       </c>
       <c r="AD43" s="3">
+        <v>441700</v>
+      </c>
+      <c r="AE43" s="3">
         <v>432200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>425400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>419600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>415200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>406900</v>
       </c>
-      <c r="AI43" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4151,8 +4247,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4214,53 +4310,56 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>309400</v>
+      </c>
+      <c r="E45" s="3">
         <v>289600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>272800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>284900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>271700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>287600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>269800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>285000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>274700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>299400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>270400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>284600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>267800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>279400</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4321,53 +4420,56 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1583600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1456200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1500800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1379600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1318200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1345400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1212100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1171900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1111200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1087300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1085500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1071000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1015700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1120400</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4428,159 +4530,165 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18494700</v>
+      </c>
+      <c r="E47" s="3">
         <v>18112200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>18603600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>18329500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>17853700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>17976000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>17891900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>18788900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>18074900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>18583900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>18561800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>16662200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>17417300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>17571100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>18389700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>17603700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>18793900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>20718200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>22758000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>22573200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>22755000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>21452300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>22452700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>21615000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>21204700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>19108500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>19847300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>19759700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>18858000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>18136700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>17118500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>17600000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>17072700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>17416900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>17734500</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3">
         <v>370000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3">
         <v>285000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="3">
         <v>240000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -4642,52 +4750,55 @@
       <c r="AK48" s="3">
         <v>0</v>
       </c>
+      <c r="AL48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7720600</v>
+      </c>
+      <c r="E49" s="3">
         <v>7609600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7489600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7362800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7245300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7114100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6986000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6877100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6742100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6613000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6491300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6371100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6260500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6136200</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>481800</v>
       </c>
       <c r="R49" s="3">
         <v>481800</v>
@@ -4705,7 +4816,7 @@
         <v>481800</v>
       </c>
       <c r="W49" s="3">
-        <v>441600</v>
+        <v>481800</v>
       </c>
       <c r="X49" s="3">
         <v>441600</v>
@@ -4749,8 +4860,11 @@
       <c r="AK49" s="3">
         <v>441600</v>
       </c>
+      <c r="AL49" s="3">
+        <v>441600</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,53 +5080,56 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1995100</v>
+      </c>
+      <c r="E52" s="3">
         <v>1998500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1065700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1726600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1640300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1575100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1039300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1079100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>838400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>833100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>325400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>769200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>754600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>751300</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5053,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="AF52" s="3">
-        <v>68600</v>
+        <v>0</v>
       </c>
       <c r="AG52" s="3">
         <v>68600</v>
@@ -5068,10 +5188,13 @@
         <v>68600</v>
       </c>
       <c r="AK52" s="3">
+        <v>68600</v>
+      </c>
+      <c r="AL52" s="3">
         <v>68500</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5300,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31562500</v>
+      </c>
+      <c r="E54" s="3">
         <v>30965900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30813700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30527600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29809300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29705300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29076200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29556800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>28298800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>28570600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>28051500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26166000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26708000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26860100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25986800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>24838800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26043200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>27850300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>29768000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>29496600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>29580100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>28112900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>29046700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>28041900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>27534200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>25351900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>25977500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>25791900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>24855400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>24133400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>23095700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>23469500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>22878700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>23182300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>23475000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,53 +5492,54 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>544500</v>
+      </c>
+      <c r="E57" s="3">
         <v>548500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>540800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>529900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>532200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>546700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>532800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>530400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>526100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>520100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>514900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>503100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>510900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>489300</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -5469,267 +5600,276 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>278000</v>
+      </c>
+      <c r="E58" s="3">
         <v>457000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>311600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>394300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>464500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>476900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>415400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>437400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>654600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>733500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>486100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>447500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>258200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>514200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>449100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>434700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>495100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>522100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>479600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>393600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>259900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>274900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>254900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>279800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>831100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>458100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>298700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>233300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>257500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>294400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>307800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>615000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>671700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>365200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>328100</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1169300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1190700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1130300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1060300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1089300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1081600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>988900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>884600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>954600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>900400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>749200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>815700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>671200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>699100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>811200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>735700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1024900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1469400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1929400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1912500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1942400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1753400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1993400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1844200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1796900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1459400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1636800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1656500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1514100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1389400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1206400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1232000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1261900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1381200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1471100</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1991800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2196300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1982700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1984500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2086000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2105200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1937100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1852400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2135400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2154000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1750200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1766300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1440400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1702700</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -5790,160 +5930,166 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3149300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2803500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2816200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2747000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2722600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2691900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2696300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2695700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1933400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1933000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1767600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1798600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1798100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1628400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1628000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1627500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1627100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1546900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1546500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1546200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1986100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1668300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1667900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1667500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1272100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1346800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1349000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1351200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1353400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1355600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1357200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1358900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>817500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1131200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1132200</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20265600</v>
+      </c>
+      <c r="E62" s="3">
         <v>19881400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20040200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20107000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>19581600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>19482700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>19137300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>20370100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19002300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19444400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20046900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17978000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>19489200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>19682800</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -5987,25 +6133,28 @@
         <v>0</v>
       </c>
       <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
         <v>51400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>51200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>50200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>49500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>50200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>49900</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6480,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25406700</v>
+      </c>
+      <c r="E66" s="3">
         <v>24881300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24839100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24838500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24390300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24279800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23770700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24918200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23071100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>23531400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23564700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21542900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>22727700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>23013800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22037200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20477200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20720100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>20956300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>21125200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>20888400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>20963100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>20280600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>20275600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>19817000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19685800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>18831600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>18683200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>18479400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>18155000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>18090000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17680500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>17930600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>17307100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>17362000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>17243600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7070,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9037400</v>
+      </c>
+      <c r="E72" s="3">
         <v>8786400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8546800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8812800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8453900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8224900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8002500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8225000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7943400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7706700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7478800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7519900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7285800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7092500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6894500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6633400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6470000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6315600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6182100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6353300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6186000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6020600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5874100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6002400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5838900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5686400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5551300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5686600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5514500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5364800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5213500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5268000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5115100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4955600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4806200</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7510,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6155800</v>
+      </c>
+      <c r="E76" s="3">
         <v>6084600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5974600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5689100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5419000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5425400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5305500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4638600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5227800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5039200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4486800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4623100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3980300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3846300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3949600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4361600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5323100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6894000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8642800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8608200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8616900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7832300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8771100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8224900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7848400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6520300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7294300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7312500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6700400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6043400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5415200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5538900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5571600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5820300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6231400</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7730,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>287700</v>
+      </c>
+      <c r="E81" s="3">
         <v>270500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>266100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>387800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>252700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>254600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>255200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>303000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>258400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>254200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>274800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>257100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>215300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>223600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>242300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>190600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>224000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>237500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>178000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>188900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>199600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>178500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>204200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>188900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>173000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>165500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>187100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>201800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>186600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>185300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>164700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>178700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>184400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>173600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1027300</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,52 +7997,53 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3">
         <v>27000</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>21000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>21000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -7906,8 +8105,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8655,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>314100</v>
+      </c>
+      <c r="E89" s="3">
         <v>420900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>350600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>306000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>307900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>431900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>336900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>340600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>374100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>350800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>391400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>286900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>326800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>477300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>371800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>357000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>296300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>397100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>377700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>358000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>330200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>371800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>397800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>309300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>425700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>343600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>333700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>343500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>263400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>423300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>340400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>320800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>234100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>382400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>343200</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,115 +8807,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-97300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-29300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17400</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-8200</v>
       </c>
       <c r="Q91" s="3">
         <v>-8200</v>
       </c>
       <c r="R91" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="S91" s="3">
         <v>-6100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-9300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-14600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-6800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9135,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-271900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-281300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-265800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-73800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-64000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-240000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>181400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-196300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>105400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-731900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-98200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-417800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-162400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-247800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-252200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-282900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-132600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-275300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-284100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>46100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-405700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-269700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-189300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-31800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-649000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-311700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-240700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-212200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-50600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-305800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>193600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-680600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-95400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-313900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-193900</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,115 +9287,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E96" s="3">
         <v>21400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>21700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>21900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>22400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>20100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>20200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>21600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>22600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>21100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>21200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>21400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>21500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>20100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-20100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-20200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-20500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-19700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-20000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-20200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-20400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-19500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-19700</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-20000</v>
       </c>
       <c r="AA96" s="3">
         <v>-20000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-18600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-18700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-18800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-17700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-17900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-18100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-18200</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-17200</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-17300</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,325 +9725,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-48100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-29600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-241000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-171800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-230800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-124500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-501000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-95100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-476700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>357000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-271700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>136800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-254800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-151700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-114700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-170300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-122800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-84700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-95600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-450500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>135800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-113300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-187100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-309000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>253300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-31300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-81100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-153300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-186700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-169500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-500100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>359600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-147600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-103300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-117400</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>13400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-6700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>9500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>9500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>13800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>9700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>4900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>110500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-158000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>63600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>66900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>30800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>46600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-19600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>17600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>10500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-97100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>79500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-86700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>44600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>35500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-41700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>56600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-13300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>14700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-33900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>23700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>14400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>9300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-22600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>22000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-53700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>43600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-6400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-29900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>30100</v>
       </c>
     </row>
